--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ILLINOIS_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ILLINOIS_2010.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C120">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C181">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C214">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C808">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C910">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C945">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1335">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1374">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1525">
